--- a/public/database/quiz/ASQ/ASQ.xlsx
+++ b/public/database/quiz/ASQ/ASQ.xlsx
@@ -3406,7 +3406,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Where do we find urban areas一in a city or countryside?
+          <t>Where do we find urban areas—in a city or countryside?
 ---
 In a city</t>
         </is>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>What piece of equipment would you use to go diving in a sea 一 an aquaplane or an aqualung?
+          <t>What piece of equipment would you use to go diving in a sea — an aquaplane or an aqualung?
 ---
 Aqualung</t>
         </is>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>A manufacturing process releases poisonous gases. What is the most important safety measure for workers at this plant一ensuring good ventilation, or appropriate footwear?
+          <t>A manufacturing process releases poisonous gases. What is the most important safety measure for workers at this plant—ensuring good ventilation, or appropriate footwear?
 ---
 Ensuring good ventilation</t>
         </is>
